--- a/examples/employees.xlsx
+++ b/examples/employees.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,20 +439,15 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Пол</t>
+          <t>Дата начала</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Дата начала</t>
+          <t>Дата приказа</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
-        <is>
-          <t>Дата приказа</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
         <is>
           <t>Номер приказа</t>
         </is>
@@ -481,20 +476,15 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>01.07.2026</t>
+          <t>30.06.2026</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
-        <is>
-          <t>30.06.2026</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
@@ -523,20 +513,15 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ж</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>01.07.2026</t>
+          <t>30.06.2026</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
-        <is>
-          <t>30.06.2026</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -565,20 +550,15 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
-        <is>
-          <t>10.07.2026</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
         <is>
           <t>19</t>
         </is>
